--- a/src/data/visualization_coding_export.xlsx
+++ b/src/data/visualization_coding_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -508,11 +508,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>spatial; structural</t>
@@ -525,16 +521,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>material; structural; material; geometry</t>
+          <t>material; structural; material; geometry; groups</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Simple Materials; Compress; Simple Materials; Shape</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Simple Materials; Compress; Simple Materials; Shape; Spatial Arrangement - Alignment</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>physics; biological</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>State Change; Living Movement</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -552,11 +556,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>spatial; geometry; material; spatial</t>
@@ -596,11 +596,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>spatial; groups; spatial</t>
@@ -613,16 +609,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>groups; framing; geometry; material; groups</t>
+          <t>geometry; material; groups; groups; framing; framing</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Spatial Arrangement - Stacking; Environment / Background; Shape; Simple Materials; Spatial Arrangement - Alignment</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Shape; Simple Materials; Spatial Arrangement - Stacking; Spatial Arrangement - Alignment; Environment / Background; Lighting</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>physics; physics</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rigid-Body Mechanics; Rigid-Body Mechanics</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,33 +644,37 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>spatial; geometry; spatial</t>
+          <t>spatial; geometry; spatial; structural</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Size; Shape; Position</t>
+          <t>Size; Shape; Position; Segment / Cut</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>material; geometry; geometry; material; structural; geometry</t>
+          <t>material; geometry; geometry; material; geometry</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Simple Materials; Shape; Shape; Simple Materials; Segment / Cut; Shape</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Simple Materials; Shape; Shape; Simple Materials; Shape</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -684,11 +692,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>material; spatial; groups; spatial</t>
@@ -701,30 +705,62 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>material; geometry; groups; groups; framing</t>
+          <t>material; geometry; groups; groups; framing; framing</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Simple Materials; Shape; Spatial Arrangement - Scattering; Spatial Arrangement - Stacking; Lighting</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Simple Materials; Shape; Spatial Arrangement - Scattering; Spatial Arrangement - Stacking; Lighting; Camera</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>physics; physics</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Rigid-Body Mechanics; Rigid-Body Mechanics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>006_The_strategic_markets_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>spatial; material; spatial</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Position; Simple Materials; Size</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>geometry; groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Shape; Spatial Arrangement - Other; Lighting; Environment / Background</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
@@ -827,16 +863,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>009_Structure_of_Daugavpils_municipality_expenditures_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Photograph of physical artefact</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Size; Segment / Cut; Position</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>material; geometry; groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Simple Materials; Shape; Spatial Arrangement - Other; Environment / Background; Lighting</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
     </row>
@@ -856,11 +916,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>spatial; spatial; spatial; spatial</t>
@@ -873,12 +929,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>geometry; material; groups; material; geometry; framing</t>
+          <t>geometry; material; groups; material; geometry; framing; framing</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Shape; Simple Materials; Spatial Arrangement - Stacking; Simple Materials; Shape; Camera</t>
+          <t>Shape; Simple Materials; Spatial Arrangement - Stacking; Simple Materials; Shape; Camera; Lighting</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -887,16 +943,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+          <t>011_Cargo_Leaders_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>spatial; framing; spatial; geometry; material</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Size; Lighting; Position; Shape; Simple Materials</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>material; groups; geometry; material; framing; framing</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Simple Materials; Spatial Arrangement - Alignment; Shape; Simple Materials; Camera; Lighting</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
     </row>
@@ -1100,11 +1180,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>spatial; groups; spatial</t>
@@ -1127,12 +1203,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>physics; physics; physics; physics</t>
+          <t>physics; physics; physics; physics; physics</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Deformable Solid Mechanics; Deformable Solid Mechanics; Rigid-Body Mechanics; Rigid-Body Mechanics</t>
+          <t>Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics; Rigid-Body Mechanics; Rigid-Body Mechanics</t>
         </is>
       </c>
     </row>
@@ -1292,11 +1368,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>spatial; material; spatial</t>
@@ -1448,11 +1520,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>structural; spatial; spatial</t>
@@ -1500,11 +1568,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>spatial; spatial</t>
@@ -1591,16 +1655,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+          <t>026_Difficulty_of_children_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>spatial; structural</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Size; Other</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>material; geometry; groups</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Simple Materials; Shape; Spatial Arrangement - Alignment</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
     </row>
@@ -1620,11 +1708,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>spatial; spatial</t>
@@ -1716,11 +1800,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>structural; spatial; spatial; spatial</t>
@@ -1743,12 +1823,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>physics; physics</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Deformable Solid Mechanics</t>
+          <t>Deformable Solid Mechanics; Deformable Solid Mechanics</t>
         </is>
       </c>
     </row>
@@ -1768,11 +1848,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>spatial; groups; spatial; spatial; structural</t>
@@ -1795,12 +1871,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>physics; physics; physics; physics; physics</t>
+          <t>physics; physics; physics; physics; physics; physics</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Weathering; Rigid-Body Mechanics; Weathering; Force Fields &amp; Particles; Force Fields &amp; Particles</t>
+          <t>Weathering; Rigid-Body Mechanics; Rigid-Body Mechanics; Weathering; Force Fields &amp; Particles; Force Fields &amp; Particles</t>
         </is>
       </c>
     </row>
@@ -1820,11 +1896,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>material; spatial; spatial; spatial; spatial; spatial; spatial</t>
@@ -1837,12 +1909,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>geometry; groups; geometry; material; geometry; material; material; framing; framing</t>
+          <t>geometry; geometry; material; groups; geometry; material; geometry; material; material; framing; framing; framing</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Shape; Spatial Arrangement - Alignment; Shape; Simple Materials; Shape; Simple Materials; Simple Materials; Environment / Background; Camera</t>
+          <t>Shape; Simple Materials; Spatial Arrangement - Alignment; Shape; Simple Materials; Shape; Simple Materials; Simple Materials; Environment / Background; Camera; Lighting</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1864,11 +1936,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>structural; material; structural; geometry; geometry; material; spatial</t>
@@ -1891,12 +1959,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>physics; physics; physics</t>
+          <t>physics; physics; physics; physics; physics; physics; physics</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics</t>
+          <t>Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics</t>
         </is>
       </c>
     </row>
@@ -1916,11 +1984,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>geometry; spatial</t>
@@ -1947,32 +2011,88 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+          <t>034_Company_Value_in_the_Stock_Exchange_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Size; Other; Position</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>geometry; material; groups</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Alignment</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>biological</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+          <t>035_Map_of_Corn_Production_Using_Candy_Corn_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Photograph of physical artefact</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>spatial; geometry; material; spatial; material</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Size; Shape; Simple Materials; Position; Simple Materials</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Spatial Arrangement - Geographical; Environment / Background; Lighting</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
     </row>
@@ -1992,11 +2112,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>spatial; geometry; geometry; spatial</t>
@@ -2009,12 +2125,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>material; geometry; groups</t>
+          <t>material; geometry; groups; framing; framing</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Simple Materials; Shape; Spatial Arrangement - Alignment</t>
+          <t>Simple Materials; Shape; Spatial Arrangement - Alignment; Lighting; Environment / Background</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2023,16 +2139,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>037</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>037_For_Every_1_Dollar_a_White_Man_Earns_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Photograph of physical artefact</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Size; Fold / Unfold; Position</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Other; Camera; Environment / Background</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -2143,16 +2283,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>040</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+          <t>040_Blaue_Blumen__Handcrafted_Offline_Data_Visualization_of_Population_Density_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Photograph of physical artefact</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>spatial; spatial</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Size; Position</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; geometry; material; spatial; framing</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Geographical; Shape; Simple Materials; Orientation; Lighting</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
     </row>
@@ -2172,11 +2336,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>spatial; spatial; material</t>
@@ -2203,16 +2363,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>042</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+          <t>042_Reasons_for_women_jurors_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Photograph of physical artefact</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Size; Segment / Cut; Position</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; material; geometry; framing</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Stacking; Simple Materials; Shape; Lighting</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
     </row>
@@ -2232,11 +2416,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>material; spatial; spatial</t>
@@ -2284,11 +2464,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>spatial; material; geometry; spatial</t>
@@ -2315,34 +2491,98 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>045</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+          <t>045_Who's_Your_Father_Star_Wars_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>spatial; spatial; material; material; geometry; spatial</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Size; Position; Simple Materials; Simple Materials; Shape; Position</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>groups; structural; spatial</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Spatial Arrangement - Alignment; Other; Orientation</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Optics</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>046</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>046_Most_Airports_Worldwide_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>spatial; spatial</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Size; Position</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>structural; material; geometry; groups; geometry; material; geometry; material</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Other; Simple Materials; Shape; Spatial Arrangement - Alignment; Shape; Simple Materials; Shape; Simple Materials</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>physics; physics</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics; Wind</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2508,11 +2748,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>spatial; spatial; geometry; material</t>
@@ -2525,16 +2761,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>geometry; structural</t>
+          <t>geometry; structural; framing</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Shape; Other</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Shape; Other; Lighting</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>biological</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2552,11 +2796,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>spatial; groups; spatial; spatial; time; groups; spatial; spatial</t>
@@ -2687,16 +2927,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>054</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+          <t>054_Commuter_Flowers_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>spatial; spatial; spatial; material; spatial; material; spatial</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Position; Orientation; Size; Material Transformations; Position; Simple Materials; Position</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>geometry; groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Shape; Spatial Arrangement - Geographical; Lighting; Environment / Background</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
     </row>
@@ -2716,11 +2980,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>groups; spatial; material; spatial; time; groups; spatial</t>
@@ -2820,11 +3080,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>spatial; material; geometry; spatial</t>
@@ -2859,16 +3115,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>058</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+          <t>058_The_Gradient_of_Naturality_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>spatial; spatial; material; spatial; spatial</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Position; Size; Simple Materials; Size; Position</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>geometry; geometry; groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Shape; Shape; Spatial Arrangement - Geographical; Lighting; Camera</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
     </row>
@@ -2940,11 +3220,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>spatial; spatial; time; spatial</t>
@@ -2979,50 +3255,146 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>061</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+          <t>061_Per_capita_freshwater_withdrawal_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Photograph of physical artefact</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Size; Inflate / Deflate; Position</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>geometry; material; geometry; material; groups; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Shape; Simple Materials; Spatial Arrangement - Alignment; Environment / Background; Lighting; Camera</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>physics; physics</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics; Fluids</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>062</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+          <t>062_The_Tallest_Tress_in_the_World_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>spatial; spatial; time; spatial</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Size; Position; Size</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>geometry; material; structural; groups; material; geometry; structural; spatial; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Other; Spatial Arrangement - Other; Simple Materials; Shape; Position; Environment / Background; Camera; Lighting</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>biological; biological; biological</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Growth; Living Movement; Living Movement</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>063</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+          <t>063_Hurricane_Size_Comparison_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>spatial; spatial; time</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Size; Position</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>spatial; geometry; material; groups; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Orientation; Shape; Simple Materials; Spatial Arrangement - Geographical; Lighting; Environment / Background; Camera</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3040,11 +3412,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>material; geometry; groups; groups</t>
@@ -3079,16 +3447,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>065</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+          <t>065_Geothermal_energy_potential_in_the_US_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>spatial; spatial; material</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Position; Position; Material Transformations</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Spatial Arrangement - Alignment; Environment / Background; Lighting</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
     </row>
@@ -3108,11 +3500,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>spatial; material; spatial</t>
@@ -3264,11 +3652,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>spatial; time; spatial</t>
@@ -3316,11 +3700,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>spatial; spatial; material; material; spatial; time</t>
@@ -3464,11 +3844,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>spatial; groups; time; spatial</t>
@@ -3516,11 +3892,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>material; spatial; spatial; groups; spatial</t>
@@ -3620,11 +3992,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>spatial; geometry; material; spatial; structural; spatial; time</t>
@@ -3647,12 +4015,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>biological; biological; physics; biological</t>
+          <t>biological; biological; biological; biological; biological; physics; biological</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Living Movement; Living Movement; Other; Living Movement</t>
+          <t>Living Movement; Living Movement; Living Movement; Living Movement; Living Movement; Other; Living Movement</t>
         </is>
       </c>
     </row>
@@ -3672,11 +4040,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Very high</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>spatial; geometry; spatial</t>
@@ -3689,12 +4053,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>geometry; material; framing; groups; geometry; material; material; geometry; framing; framing</t>
+          <t>geometry; material; structural; groups; geometry; material; framing; framing; framing</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Shape; Simple Materials; Lighting; Spatial Arrangement - Alignment; Shape; Simple Materials; Simple Materials; Shape; Environment / Background; Camera</t>
+          <t>Shape; Simple Materials; Break / Shatter; Spatial Arrangement - Alignment; Shape; Simple Materials; Environment / Background; Camera; Lighting</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3703,7 +4067,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>078_Births_and_Deaths_Rate_Sotiris_Dynamic.json</t>
+          <t>078_Births_and_Deaths_Rate_Consolidated_Dynamic.json</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3716,11 +4080,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>material; groups; groups</t>
@@ -3733,29 +4093,29 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>spatial; groups; groups; framing</t>
+          <t>spatial; groups; groups; framing; framing; framing</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Position; Other; Spatial Arrangement - Stacking; Environment / Background</t>
+          <t>Position; Other; Spatial Arrangement - Stacking; Environment / Background; Camera; Lighting</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>physics; physics; physics</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Rigid-Body Mechanics</t>
+          <t>Rigid-Body Mechanics; Rigid-Body Mechanics; Rigid-Body Mechanics</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>079_Elephant_Rocket_Fuel_Sotiris_Dynamic.json</t>
+          <t>079_Elephant_Rocket_Fuel_Consolidated_Dynamic.json</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3768,29 +4128,25 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>spatial; groups; groups</t>
+          <t>material; geometry; groups; groups</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Size; Count; Spatial Arrangement - Scattering</t>
+          <t>Shape; Count; Spatial Arrangement - Scattering</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>geometry; material; groups; geometry; material; spatial; spatial; geometry; material</t>
+          <t>groups; geometry; material; spatial; spatial; geometry; material</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Shape; Spatial Arrangement - Scattering; Shape; Simple Materials; Size; Position; Shape; Simple Materials</t>
+          <t>Spatial Arrangement - Scattering; Shape; Simple Materials; Size; Position; Shape; Simple Materials</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3820,11 +4176,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>groups; time</t>
@@ -3837,12 +4189,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>geometry; material; spatial; framing; spatial</t>
+          <t>geometry; material; spatial; framing; spatial; framing</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Shape; Simple Materials; Position; Environment / Background; Orientation</t>
+          <t>Shape; Simple Materials; Position; Environment / Background; Orientation; Lighting</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3872,11 +4224,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>spatial; groups; spatial; time; spatial; spatial</t>
@@ -3889,22 +4237,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>material; geometry; groups; geometry; material; geometry; material; framing; framing</t>
+          <t>material; geometry; spatial; groups; geometry; material; geometry; material; spatial; framing; framing; framing</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Simple Materials; Shape; Spatial Arrangement - Stacking; Shape; Simple Materials; Shape; Simple Materials; Environment / Background; Camera</t>
+          <t>Simple Materials; Shape; Position; Spatial Arrangement - Stacking; Shape; Simple Materials; Shape; Simple Materials; Position; Environment / Background; Camera; Lighting</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>physics; physics; physics; physics</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Force Fields &amp; Particles</t>
+          <t>Force Fields &amp; Particles; Force Fields &amp; Particles; Rigid-Body Mechanics; Other</t>
         </is>
       </c>
     </row>
@@ -3924,11 +4272,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>spatial; spatial; groups; spatial; time; spatial; material; geometry</t>
@@ -4028,11 +4372,7 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>spatial; spatial; spatial</t>
@@ -4059,16 +4399,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>085</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+          <t>085_Europe's_$2_Trillion_Infrastructure_Investment_Deficit_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>spatial; spatial; structural</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Size; Position; Break / Shatter</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>geometry; material; groups</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Alignment</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
     </row>
@@ -4088,11 +4452,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>groups; time; groups</t>
@@ -4192,11 +4552,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>material; spatial; groups; groups; time; spatial</t>
@@ -4224,7 +4580,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Rigid-Body Mechanics; Other; Rigid-Body Mechanics</t>
+          <t>Rigid-Body Mechanics; Rigid-Body Mechanics; Rigid-Body Mechanics</t>
         </is>
       </c>
     </row>
@@ -4244,11 +4600,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>geometry; spatial; spatial; spatial; spatial; spatial</t>
@@ -4348,11 +4700,7 @@
           <t>Dynamic</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>structural; structural; time; spatial; structural</t>
@@ -4375,12 +4723,564 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
+          <t>physics; physics; physics; physics</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>092_Total_Mass_of_Biosphere_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>spatial; material; time; spatial; spatial</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Size; Simple Materials; Position; Size</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>geometry; spatial; spatial; groups; geometry; material; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Shape; Size; Orientation; Spatial Arrangement - Other; Shape; Simple Materials; Environment / Background; Camera; Lighting</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>physics; physics</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Rigid-Body Mechanics; Rigid-Body Mechanics</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>093_Antibiotics_Consumption_Levels_in_Europe_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>spatial; spatial; material</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Size; Position; Simple Materials</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>geometry; material; geometry; groups; material; geometry; material; geometry; framing; framing</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Shape; Spatial Arrangement - Alignment; Simple Materials; Shape; Simple Materials; Shape; Camera; Lighting</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>094_Microorganisms_in_Perspective_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>spatial; geometry; material; spatial; time; spatial</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Size; Simple Materials; Position; Size</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>structural; groups; geometry; material; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Other; Spatial Arrangement - Alignment; Shape; Simple Materials; Lighting; Environment / Background; Camera</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>biological</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Living Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>095_The_Biggest_Buildings_That_Do_Not_Exist_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>geometry; material; spatial; spatial; time; material; spatial</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Size; Position; Simple Materials; Size</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Other; Environment / Background; Lighting; Camera</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>096_World_in_Slices_Sotiris_Static.json</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Size; Segment / Cut; Position</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; geometry; material; framing; framing</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Other; Shape; Simple Materials; Lighting; Camera</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>097_Smallpox_Deaths_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>spatial; material; structural; spatial; time</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Size; Simple Materials; Other; Position</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>groups; groups; framing; framing</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Spatial Arrangement - Other; Spatial Arrangement - Other; Camera; Lighting</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Burning &amp; Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>098_Billionaires_Earnings_Consolidated_Dynamic.json</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; spatial</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Count; Size</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>structural; spatial; geometry; material; spatial; groups; spatial; groups; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Other; Position; Shape; Simple Materials; Position; Spatial Arrangement - Scattering; Position; Spatial Arrangement - Other; Environment / Background; Camera; Lighting</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>biological</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Living Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>099_What_Creatives_Do_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Size; Break / Shatter; Position</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>geometry; material; structural; material; groups; geometry; material; framing</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Other; Simple Materials; Spatial Arrangement - Other; Shape; Simple Materials; Lighting</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100_Europe's_Chocolate_Consumption_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3D render</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>spatial; structural; spatial</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Size; Other; Position</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>material; groups</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Simple Materials; Spatial Arrangement - Other</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101_How_Much_Power_Do_Data_Centers_Use_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>spatial; material; spatial</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Size; Simple Materials; Position</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>geometry; groups; geometry; material; framing</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Shape; Spatial Arrangement - Stacking; Shape; Simple Materials; Camera</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>physics; physics</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Optics; Optics</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102_Which_Countries_Buy_the_Most_US_Coal_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>spatial; structural; material; spatial</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Size; Break / Shatter; Position</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; framing; framing; framing</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Other; Lighting; Environment / Background; Camera</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Deformable Solid Mechanics</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103_Countries_With_the_Highest_Remittance_Costs_Consolidated_Static.json</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Graphic design - Illustration</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>spatial; groups; spatial</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Size; Count; Position</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>geometry; material; groups; material; structural</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Shape; Simple Materials; Spatial Arrangement - Other; Simple Materials</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
           <t>physics; physics; physics</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Deformable Solid Mechanics; Deformable Solid Mechanics; Deformable Solid Mechanics</t>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Rigid-Body Mechanics; Force Fields &amp; Particles; Force Fields &amp; Particles</t>
         </is>
       </c>
     </row>
